--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:J39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,12 +483,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-111987</t>
+          <t>I-16168</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140106</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -503,22 +503,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.7653258</t>
+          <t>-6.8216999</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.8528915</t>
+          <t>-79.8550922</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Avenida Fernando Belaunde Terry / Avenida José Eufemio Lora y Lora</t>
+          <t>Carretera Monsefú - Chiclayo / LA-784</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -535,12 +535,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-18504</t>
+          <t>I-225128</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -555,27 +555,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7652441</t>
+          <t>-6.7708286</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.8524433</t>
+          <t>-79.7870572</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Fernando Belaunde Terry / Manuel Gustavo Cornejo</t>
+          <t>Avenida Bolivia / Avenida Perú</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>l-261576</t>
+          <t>I-232602</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -607,22 +607,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.7809457</t>
+          <t>-6.7702521</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.8370332</t>
+          <t>-79.7821132</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>José Rodriguez Trigoso</t>
+          <t>Avenida Perú / Calle Los Algarrobos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -639,12 +639,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>l-336665</t>
+          <t>I-232650</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -659,22 +659,22 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.7878966</t>
+          <t>-6.7700987</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.8702939</t>
+          <t>-79.778826</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Prolongación Avenida Francisco Bolognesi</t>
+          <t>Avenida San Francisco de Asís / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -691,12 +691,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>l-436476</t>
+          <t>I-232878</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -711,27 +711,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.766354</t>
+          <t>-6.7703867</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.84175</t>
+          <t>-79.7830318</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>AV. LUIS GONZALES CON CALLE ARICA</t>
+          <t>Avenida Perú / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -743,12 +743,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>l-37226</t>
+          <t>I-232941</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -763,22 +763,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.7841629</t>
+          <t>-6.7699818</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.8336456</t>
+          <t>-79.7790817</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Chinchaysuyo / Avenida Fitzcarrald / Avenida Víctor Raúl Haya de la Torre</t>
+          <t>Avenida Perú / Jirón Leoncio Prado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -795,12 +795,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>l-439186</t>
+          <t>I-225105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -815,27 +815,27 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.7813816</t>
+          <t>-6.770017</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.8375174</t>
+          <t>-79.7777271</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Arizola / Manuel Gutierrez</t>
+          <t>Avenida San Francisco de Asís / Calle s / n</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -847,12 +847,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>l-439187</t>
+          <t>I-822920</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -867,22 +867,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>REQUE</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.781149</t>
+          <t>-6.8602751</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.837482</t>
+          <t>-79.8115463</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Arizola / Pasaje José Rodriguez Trigoso</t>
+          <t>Jirón Atahualpa / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -899,7 +899,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>l-479983</t>
+          <t>I-261576</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -924,17 +924,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.7758318</t>
+          <t>-6.7809457</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.8366578</t>
+          <t>-79.8370332</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Nieto / Mariscal Castilla</t>
+          <t>José Rodriguez Trigoso / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -951,12 +951,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>l-480034</t>
+          <t>I-36900</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140106</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -971,22 +971,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.7648822</t>
+          <t>-6.8404659</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.8193217</t>
+          <t>-79.8596739</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Indoamérica / Trébol Rojo</t>
+          <t>Carretera Monsefú - Chiclayo / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1003,12 +1003,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>l-480060</t>
+          <t>I-36913</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140106</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1023,22 +1023,22 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>LA VICTORIA</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.764908</t>
+          <t>-6.8401535</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.8197696</t>
+          <t>-79.8596106</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Fanny Abanto / Indoamérica</t>
+          <t>Carretera Monsefú - Chiclayo / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1055,12 +1055,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>l-480273</t>
+          <t>I-581136</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140108</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1075,27 +1075,27 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>MONSEFU</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.7684675</t>
+          <t>-6.8757112</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.8464539</t>
+          <t>-79.866538</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Jr. Diego Ferre / Melitón Carvajal</t>
+          <t>Calle Sáenz Peña / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1107,7 +1107,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>l-480443</t>
+          <t>I-479983</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1132,17 +1132,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.7645366</t>
+          <t>-6.7758318</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.8590042</t>
+          <t>-79.8366578</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Escrivá de Balaguer / Calle Sicuani</t>
+          <t>Avenida Mariscal Nieto / Mariscal Castilla</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1159,7 +1159,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>l-480801</t>
+          <t>I-480273</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1184,17 +1184,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.7646995</t>
+          <t>-6.7684675</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.8591693</t>
+          <t>-79.8464539</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida Escrivá de Balaguer / Calle Manuel González Prada</t>
+          <t>Jirón Diego Ferre / Melitón Carvajal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1211,7 +1211,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>l-480802</t>
+          <t>I-480805</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1236,17 +1236,17 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.7647798</t>
+          <t>-6.7642803</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-79.8593258</t>
+          <t>-79.8594008</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida Escriva de Balaguer / Calle Manuel González Prada</t>
+          <t>Avenida Escrivá de Balaguer / Calle Mariano Melgar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1263,7 +1263,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>l-480805</t>
+          <t>I-481341</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1288,17 +1288,17 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.7642803</t>
+          <t>-6.7803733</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-79.8594008</t>
+          <t>-79.8542602</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Avenida Escrivá de Balaguer / Calle Mariano Melgar</t>
+          <t>Calle Prolongación Avenida Francisco Bolognesi / Calle Piura</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1315,12 +1315,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>l-480806</t>
+          <t>I-235222</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1335,22 +1335,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>REQUE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.7643675</t>
+          <t>-6.8409089</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.8595627</t>
+          <t>-79.7906501</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Auxiliar Avenida Escriva de Balaguer / Calle Mariano Melgar</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1367,7 +1367,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>l-481341</t>
+          <t>I-704582</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1392,17 +1392,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.7803733</t>
+          <t>-6.7658243</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.8542602</t>
+          <t>-79.8527996</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle Piura / Avenida José Eufemio Lora y Lora</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>l-481344</t>
+          <t>I-825895</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1444,17 +1444,17 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.7801536</t>
+          <t>-6.7668626</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.8543179</t>
+          <t>-79.8368214</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Prolongación Avenida Francisco Bolognesi</t>
+          <t>Calle 7 de Enero / Calle Arica</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1471,12 +1471,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>l-542551</t>
+          <t>I-822962</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140114</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1491,22 +1491,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>SANTA ROSA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.7758969</t>
+          <t>-6.8549405</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-79.8364112</t>
+          <t>-79.9048364</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Avenida Francisco Bolognesi</t>
+          <t>LA-781 / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1523,12 +1523,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>l-542552</t>
+          <t>I-741350</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1543,22 +1543,22 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.7757634</t>
+          <t>-6.7849385</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-79.8364063</t>
+          <t>-79.685365</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Nieto</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1575,7 +1575,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>l-633149</t>
+          <t>I-73596</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1600,22 +1600,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.7815863</t>
+          <t>-6.7668619</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.8369118</t>
+          <t>-79.8482705</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Manuel Gutierrez</t>
+          <t>Avenida José Eufemio Lora y Lora / José Carlos Mariátegui</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -1627,12 +1627,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>l-633151</t>
+          <t>I-7114</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140112</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1647,27 +1647,27 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>PIMENTEL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.7815555</t>
+          <t>-6.7699826</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-79.837003</t>
+          <t>-79.8795769</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Manuel Gutierrez</t>
+          <t>Carretera Chiclayo - Ciudad de Dios - San José / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -1679,12 +1679,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>l-633152</t>
+          <t>I-729871</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140112</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,27 +1699,27 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>PIMENTEL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.7814596</t>
+          <t>-6.8210361</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-79.8372865</t>
+          <t>-79.9033915</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Manuel Gutierrez</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1731,12 +1731,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>l-633154</t>
+          <t>I-555471</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1751,27 +1751,27 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.7810664</t>
+          <t>-6.7616288</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-79.8370581</t>
+          <t>-79.7091539</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Pasaje José Rodriguez Trigoso</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -1783,12 +1783,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>l-704582</t>
+          <t>I-223903</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1803,27 +1803,27 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-6.7658243</t>
+          <t>-6.6908033</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.8527996</t>
+          <t>-79.7024575</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>l-704583</t>
+          <t>I-223904</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1855,27 +1855,27 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.765783</t>
+          <t>-6.6902876</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.8527433</t>
+          <t>-79.693757</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -1887,12 +1887,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>l-7104</t>
+          <t>I-223916</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1907,27 +1907,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-6.764602</t>
+          <t>-6.6869884</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-79.8591355</t>
+          <t>-79.705396</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Avenida Escrivá de Balaguer / Calle Sicuani</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -1939,12 +1939,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>l-73258</t>
+          <t>I-223918</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1959,27 +1959,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.76545</t>
+          <t>-6.6922831</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-79.8527607</t>
+          <t>-79.7036186</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora / Piura</t>
+          <t>Camino Luya / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -1991,12 +1991,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>l-73259</t>
+          <t>I-223920</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2011,27 +2011,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6.7655006</t>
+          <t>-6.6906458</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-79.8528385</t>
+          <t>-79.7052787</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora / Piura</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2043,12 +2043,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>l-73263</t>
+          <t>I-36582</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2063,27 +2063,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>REQUE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-6.7657814</t>
+          <t>-6.8657542</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-79.8529184</t>
+          <t>-79.8189836</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Justicia / Piura</t>
+          <t>Calle Elías Aguirre / Calle Miguel Grau</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2095,12 +2095,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>l-73268</t>
+          <t>I-766265</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140113</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2115,27 +2115,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>REQUE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-6.7657239</t>
+          <t>-6.8238853</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-79.8529129</t>
+          <t>-79.752228</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Piura</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2147,7 +2147,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>l-73590</t>
+          <t>I-336665</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2172,17 +2172,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.7651464</t>
+          <t>-6.7878966</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-79.8529021</t>
+          <t>-79.8702939</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Avenida Fernando Belaunde Terry / Avenida José Eufemio Lora y Lora</t>
+          <t>Prolongación Avenida Francisco Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2199,12 +2199,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>l-73594</t>
+          <t>I-726150</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140112</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2219,27 +2219,27 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>PIMENTEL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-6.7685212</t>
+          <t>-6.7991232</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-79.8465143</t>
+          <t>-79.9205609</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora / Jr. Diego Ferre</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2251,12 +2251,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>l-73598</t>
+          <t>I-726156</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140112</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2271,27 +2271,27 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>PIMENTEL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.7653435</t>
+          <t>-6.803997</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-79.8528036</t>
+          <t>-79.9208842</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Avenida Fernando Belaunde Terry / Avenida José Eufemio Lora y Lora</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2303,12 +2303,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>l-73867</t>
+          <t>I-223644</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2323,27 +2323,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-6.7653957</t>
+          <t>-6.779411</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-79.8528813</t>
+          <t>-79.6811213</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2355,12 +2355,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>l-73877</t>
+          <t>I-223630</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140120</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2375,27 +2375,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>TUMAN</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-6.7656882</t>
+          <t>-6.7795696</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-79.8525763</t>
+          <t>-79.6801786</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2407,12 +2407,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>l-73878</t>
+          <t>I-642795</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>140101</t>
+          <t>140118</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2427,290 +2427,30 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>CHICLAYO</t>
+          <t>POMALCA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-6.7655712</t>
+          <t>-6.8209849</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-79.8527983</t>
+          <t>-79.7855517</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>l-74130</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-6.7800766</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-79.8543607</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Piura / Prolongación Avenida Francisco Bolognesi</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>l-74726</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>-6.7841707</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>-79.83377</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Avenida Chinchaysuyo / Avenida Víctor Raúl Haya de la Torre</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>l-792522</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>-6.7758585</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>-79.8367504</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Avenida Francisco Bolognesi / Avenida Mariscal Nieto</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>l-792525</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>-6.7758939</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>-79.8368502</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Avenida Francisco Bolognesi / Avenida Mariscal Nieto</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>l-825895</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>-6.7668626</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>-79.8368214</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Calle 7 de Enero / Calle Arica</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
         <is>
           <t>140101</t>
         </is>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J39"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +2456,318 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>I-36516</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-6.8810225</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-79.8594709</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>I-645602</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-6.8670564</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-79.8900134</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>I-645604</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-6.8664225</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-79.8848045</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>I-645605</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-6.85918</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-79.8868474</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>I-724649</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>140112</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PIMENTEL</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>-6.8197773</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>-79.8947424</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>I-7049</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>140120</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>TUMAN</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>-6.7946816</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>-79.6875053</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -570,7 +570,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Bolivia / Avenida Perú</t>
+          <t>Avenida Bolivia / Avenida Perú / Avenida San Francisco de Asís</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Perú / Calle s / n</t>
+          <t>Avenida Perú / Avenida San Francisco de Asís</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -778,7 +778,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Perú / Jirón Leoncio Prado</t>
+          <t>Avenida Perú / Avenida San Francisco de Asís / Jirón Leoncio Prado</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís / Calle s / n</t>
+          <t>Avenida San Francisco de Asís / Jirón Aurelio Ballenas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Jirón Atahualpa / Calle s / n</t>
+          <t>Calle Francisco Bolognesi / Jirón Atahualpa</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>José Rodriguez Trigoso / Calle s / n</t>
+          <t>José Rodriguez Trigoso / Pasaje José Rodriguez Trigoso</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Nieto / Mariscal Castilla</t>
+          <t>Avenida Francisco Bolognesi / Avenida Mariscal Nieto / Mariscal Castilla</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Jirón Diego Ferre / Melitón Carvajal</t>
+          <t>Avenida José Eufemio Lora y Lora / Jirón Diego Ferre / Melitón Carvajal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle Piura / Avenida José Eufemio Lora y Lora</t>
+          <t>Justicia / Piura</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1610,7 +1610,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora / José Carlos Mariátegui</t>
+          <t>Avenida José Eufemio Lora y Lora / Calle Bernardo Alcedo / José Carlos Mariátegui</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2763,6 +2763,526 @@
         </is>
       </c>
       <c r="J45" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>I-9271</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>140106</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>-6.7892645</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>-79.8469799</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Avenida Chinchaysuyo / Avenida Miguel Grau</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>I-732278</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>140106</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LA VICTORIA</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-6.8261457</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-79.8756368</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>I-667432</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-6.8540783</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-79.8720089</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>I-645606</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-6.860875</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-79.8859891</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>I-645804</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>-6.8750272</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>-79.8986587</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>I-645805</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>140108</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>MONSEFU</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>-6.8689665</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>-79.897498</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>I-579094</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>140118</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>POMALCA</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-6.7716644</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>-79.7928375</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Avenida San Francisco de Asís / Calle Héroes del Cenepa</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>I-7050</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>140120</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>TUMAN</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-6.7959262</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-79.6871373</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>I-223593</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>140120</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>TUMAN</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>-6.7798068</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-79.6788031</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>140101</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>I-181438</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>140120</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>TUMAN</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-6.7499562</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>-79.6996674</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Avenida El Tren / Calle Tumbes</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
         <is>
           <t>140101</t>
         </is>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-16168</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>140106</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-6.8216999</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-225128</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-6.7708286</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-232602</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-6.7702521</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-232650</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-6.7700987</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-232878</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-6.7703867</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-232941</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-6.7699818</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-225105</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-6.770017</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-822920</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>140113</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>REQUE</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-6.8602751</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-261576</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-6.7809457</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-36900</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>140106</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-6.8404659</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-36913</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>140106</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-6.8401535</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-581136</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-6.8757112</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-479983</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-6.7758318</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-480273</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-6.7684675</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-480805</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-6.7642803</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-481341</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-6.7803733</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-235222</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>140113</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>REQUE</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-6.8409089</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-704582</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-6.7658243</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-825895</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-6.7668626</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-822962</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>140114</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>SANTA ROSA</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-6.8549405</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-741350</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-6.7849385</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-73596</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-6.7668619</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-7114</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>140112</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PIMENTEL</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-6.7699826</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-729871</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>140112</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PIMENTEL</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-6.8210361</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-555471</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-6.7616288</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-223903</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-6.6908033</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-223904</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-6.6902876</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-223916</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-6.6869884</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-223918</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-6.6922831</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-223920</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-6.6906458</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-36582</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>140113</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>REQUE</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-6.8657542</t>
@@ -2084,40 +1929,35 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>I-766265</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>140113</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>REQUE</t>
-        </is>
-      </c>
       <c r="F33" t="inlineStr">
         <is>
           <t>-6.8238853</t>
@@ -2136,40 +1976,35 @@
       <c r="I33" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>I-336665</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>140101</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
       <c r="F34" t="inlineStr">
         <is>
           <t>-6.7878966</t>
@@ -2188,40 +2023,35 @@
       <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>I-726150</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>140112</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>PIMENTEL</t>
-        </is>
-      </c>
       <c r="F35" t="inlineStr">
         <is>
           <t>-6.7991232</t>
@@ -2240,40 +2070,35 @@
       <c r="I35" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>I-726156</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>140112</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>PIMENTEL</t>
-        </is>
-      </c>
       <c r="F36" t="inlineStr">
         <is>
           <t>-6.803997</t>
@@ -2292,40 +2117,35 @@
       <c r="I36" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>I-223644</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F37" t="inlineStr">
         <is>
           <t>-6.779411</t>
@@ -2344,40 +2164,35 @@
       <c r="I37" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>I-223630</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F38" t="inlineStr">
         <is>
           <t>-6.7795696</t>
@@ -2396,40 +2211,35 @@
       <c r="I38" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>I-642795</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F39" t="inlineStr">
         <is>
           <t>-6.8209849</t>
@@ -2448,40 +2258,35 @@
       <c r="I39" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>I-36516</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F40" t="inlineStr">
         <is>
           <t>-6.8810225</t>
@@ -2500,40 +2305,35 @@
       <c r="I40" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>I-645602</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F41" t="inlineStr">
         <is>
           <t>-6.8670564</t>
@@ -2552,40 +2352,35 @@
       <c r="I41" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>I-645604</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F42" t="inlineStr">
         <is>
           <t>-6.8664225</t>
@@ -2604,40 +2399,35 @@
       <c r="I42" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>I-645605</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F43" t="inlineStr">
         <is>
           <t>-6.85918</t>
@@ -2656,40 +2446,35 @@
       <c r="I43" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>I-724649</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>140112</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>PIMENTEL</t>
-        </is>
-      </c>
       <c r="F44" t="inlineStr">
         <is>
           <t>-6.8197773</t>
@@ -2708,40 +2493,35 @@
       <c r="I44" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>I-7049</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F45" t="inlineStr">
         <is>
           <t>-6.7946816</t>
@@ -2760,40 +2540,35 @@
       <c r="I45" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>I-9271</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>140106</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
       <c r="F46" t="inlineStr">
         <is>
           <t>-6.7892645</t>
@@ -2812,40 +2587,35 @@
       <c r="I46" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>I-732278</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>140106</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>LA VICTORIA</t>
-        </is>
-      </c>
       <c r="F47" t="inlineStr">
         <is>
           <t>-6.8261457</t>
@@ -2864,40 +2634,35 @@
       <c r="I47" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>I-667432</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F48" t="inlineStr">
         <is>
           <t>-6.8540783</t>
@@ -2916,40 +2681,35 @@
       <c r="I48" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>I-645606</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F49" t="inlineStr">
         <is>
           <t>-6.860875</t>
@@ -2968,40 +2728,35 @@
       <c r="I49" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>I-645804</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
           <t>-6.8750272</t>
@@ -3020,40 +2775,35 @@
       <c r="I50" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>I-645805</t>
         </is>
       </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>140108</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>MONSEFU</t>
-        </is>
-      </c>
       <c r="F51" t="inlineStr">
         <is>
           <t>-6.8689665</t>
@@ -3072,40 +2822,35 @@
       <c r="I51" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>I-579094</t>
         </is>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>140118</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>POMALCA</t>
-        </is>
-      </c>
       <c r="F52" t="inlineStr">
         <is>
           <t>-6.7716644</t>
@@ -3124,40 +2869,35 @@
       <c r="I52" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>I-7050</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F53" t="inlineStr">
         <is>
           <t>-6.7959262</t>
@@ -3176,40 +2916,35 @@
       <c r="I53" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>I-223593</t>
         </is>
       </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-6.7798068</t>
@@ -3228,40 +2963,35 @@
       <c r="I54" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>140101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>LAMBAYEQUE</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>CHICLAYO</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>I-181438</t>
         </is>
       </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>140120</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>LAMBAYEQUE</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>CHICLAYO</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>TUMAN</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>-6.7499562</t>
@@ -3280,11 +3010,6 @@
       <c r="I55" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>140101</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
+++ b/Intersecciones/excels/LAMBAYEQUE-CHICLAYO-CHICLAYO.xlsx
@@ -486,27 +486,27 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-16168</t>
+          <t>I-9271</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-6.8216999</t>
+          <t>-6.7892645</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-79.8550922</t>
+          <t>-79.8469799</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Carretera Monsefú - Chiclayo / LA-784</t>
+          <t>Avenida Chinchaysuyo / Avenida Miguel Grau</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -533,27 +533,27 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-225128</t>
+          <t>I-825895</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-6.7708286</t>
+          <t>-6.7668626</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-79.7870572</t>
+          <t>-79.8368214</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Avenida Bolivia / Avenida Perú / Avenida San Francisco de Asís</t>
+          <t>Calle 7 de Enero / Calle Arica</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-232602</t>
+          <t>I-822962</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-6.7702521</t>
+          <t>-6.8549405</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-79.7821132</t>
+          <t>-79.9048364</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Perú / Calle Los Algarrobos</t>
+          <t>LA-781 / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-232650</t>
+          <t>I-822920</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-6.7700987</t>
+          <t>-6.8602751</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-79.778826</t>
+          <t>-79.8115463</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís / Calle s / n</t>
+          <t>Jirón Atahualpa / Calle s / n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-232878</t>
+          <t>I-766265</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-6.7703867</t>
+          <t>-6.8238853</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-79.7830318</t>
+          <t>-79.752228</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Avenida Perú / Avenida San Francisco de Asís</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-232941</t>
+          <t>I-741350</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-6.7699818</t>
+          <t>-6.7849385</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-79.7790817</t>
+          <t>-79.685365</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Avenida Perú / Avenida San Francisco de Asís / Jirón Leoncio Prado</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,22 +768,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-225105</t>
+          <t>I-73596</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-6.770017</t>
+          <t>-6.7668619</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-79.7777271</t>
+          <t>-79.8482705</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís / Jirón Aurelio Ballenas</t>
+          <t>Avenida José Eufemio Lora y Lora / José Carlos Mariátegui</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -815,22 +815,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-822920</t>
+          <t>I-732278</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-6.8602751</t>
+          <t>-6.8261457</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-79.8115463</t>
+          <t>-79.8756368</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Calle Francisco Bolognesi / Jirón Atahualpa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -862,27 +862,27 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-261576</t>
+          <t>I-729871</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-6.7809457</t>
+          <t>-6.8210361</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-79.8370332</t>
+          <t>-79.9033915</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>José Rodriguez Trigoso / Pasaje José Rodriguez Trigoso</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -909,27 +909,27 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-36900</t>
+          <t>I-726156</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-6.8404659</t>
+          <t>-6.803997</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-79.8596739</t>
+          <t>-79.9208842</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Carretera Monsefú - Chiclayo / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -956,27 +956,27 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-36913</t>
+          <t>I-726150</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-6.8401535</t>
+          <t>-6.7991232</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-79.8596106</t>
+          <t>-79.9205609</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Carretera Monsefú - Chiclayo / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1003,22 +1003,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-581136</t>
+          <t>I-724649</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-6.8757112</t>
+          <t>-6.8197773</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-79.866538</t>
+          <t>-79.8947424</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Calle Sáenz Peña / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1050,27 +1050,27 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-479983</t>
+          <t>I-7114</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-6.7758318</t>
+          <t>-6.7699826</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-79.8366578</t>
+          <t>-79.8795769</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Avenida Francisco Bolognesi / Avenida Mariscal Nieto / Mariscal Castilla</t>
+          <t>Carretera Chiclayo - Ciudad de Dios - San José / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1097,27 +1097,27 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-480273</t>
+          <t>I-7050</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-6.7684675</t>
+          <t>-6.7959262</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-79.8464539</t>
+          <t>-79.6871373</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora / Jirón Diego Ferre / Melitón Carvajal</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1144,27 +1144,27 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-480805</t>
+          <t>I-7049</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-6.7642803</t>
+          <t>-6.7946816</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-79.8594008</t>
+          <t>-79.6875053</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Avenida Escrivá de Balaguer / Calle Mariano Melgar</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1191,22 +1191,22 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-481341</t>
+          <t>I-704582</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.7803733</t>
+          <t>-6.7658243</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-79.8542602</t>
+          <t>-79.8527996</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Calle Prolongación Avenida Francisco Bolognesi / Calle Piura</t>
+          <t>Calle Piura / Avenida José Eufemio Lora y Lora</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-235222</t>
+          <t>I-667432</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.8409089</t>
+          <t>-6.8540783</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-79.7906501</t>
+          <t>-79.8720089</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1285,27 +1285,27 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-704582</t>
+          <t>I-645805</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-6.7658243</t>
+          <t>-6.8689665</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-79.8527996</t>
+          <t>-79.897498</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Justicia / Piura</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1332,27 +1332,27 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-825895</t>
+          <t>I-645804</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-6.7668626</t>
+          <t>-6.8750272</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-79.8368214</t>
+          <t>-79.8986587</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Calle 7 de Enero / Calle Arica</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1379,27 +1379,27 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-822962</t>
+          <t>I-645606</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-6.8549405</t>
+          <t>-6.860875</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-79.9048364</t>
+          <t>-79.8859891</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>LA-781 / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-741350</t>
+          <t>I-645605</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-6.7849385</t>
+          <t>-6.85918</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-79.685365</t>
+          <t>-79.8868474</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1446,7 +1446,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -1473,22 +1473,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-73596</t>
+          <t>I-645604</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-6.7668619</t>
+          <t>-6.8664225</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-79.8482705</t>
+          <t>-79.8848045</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Avenida José Eufemio Lora y Lora / Calle Bernardo Alcedo / José Carlos Mariátegui</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1520,22 +1520,22 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-7114</t>
+          <t>I-645602</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-6.7699826</t>
+          <t>-6.8670564</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-79.8795769</t>
+          <t>-79.8900134</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Carretera Chiclayo - Ciudad de Dios - San José / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-729871</t>
+          <t>I-642795</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-6.8210361</t>
+          <t>-6.8209849</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-79.9033915</t>
+          <t>-79.7855517</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,22 +1614,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-555471</t>
+          <t>I-581136</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-6.7616288</t>
+          <t>-6.8757112</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-79.7091539</t>
+          <t>-79.866538</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Sáenz Peña / Calle s / n</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1661,22 +1661,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-223903</t>
+          <t>I-579094</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-6.6908033</t>
+          <t>-6.7716644</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.7024575</t>
+          <t>-79.7928375</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida San Francisco de Asís / Calle Héroes del Cenepa</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-223904</t>
+          <t>I-555471</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-6.6902876</t>
+          <t>-6.7616288</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-79.693757</t>
+          <t>-79.7091539</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1755,27 +1755,27 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-223916</t>
+          <t>I-481341</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-6.6869884</t>
+          <t>-6.7803733</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-79.705396</t>
+          <t>-79.8542602</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Prolongación Avenida Francisco Bolognesi / Calle Piura</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1802,27 +1802,27 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-223918</t>
+          <t>I-480805</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-6.6922831</t>
+          <t>-6.7642803</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-79.7036186</t>
+          <t>-79.8594008</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Camino Luya / Calle s / n</t>
+          <t>Avenida Escrivá de Balaguer / Calle Mariano Melgar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1849,27 +1849,27 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-223920</t>
+          <t>I-480273</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-6.6906458</t>
+          <t>-6.7684675</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-79.7052787</t>
+          <t>-79.8464539</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Jirón Diego Ferre / Melitón Carvajal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-36582</t>
+          <t>I-479983</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-6.8657542</t>
+          <t>-6.7758318</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-79.8189836</t>
+          <t>-79.8366578</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Calle Elías Aguirre / Calle Miguel Grau</t>
+          <t>Avenida Mariscal Nieto / Mariscal Castilla</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1943,27 +1943,27 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-766265</t>
+          <t>I-36913</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-6.8238853</t>
+          <t>-6.8401535</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-79.752228</t>
+          <t>-79.8596106</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Carretera Monsefú - Chiclayo / Calle s / n</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-336665</t>
+          <t>I-36900</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-6.7878966</t>
+          <t>-6.8404659</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-79.8702939</t>
+          <t>-79.8596739</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Prolongación Avenida Francisco Bolognesi / Calle s / n</t>
+          <t>Carretera Monsefú - Chiclayo / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-726150</t>
+          <t>I-36582</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-6.7991232</t>
+          <t>-6.8657542</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-79.9205609</t>
+          <t>-79.8189836</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Calle Elías Aguirre / Calle Miguel Grau</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-726156</t>
+          <t>I-36516</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.803997</t>
+          <t>-6.8810225</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-79.9208842</t>
+          <t>-79.8594709</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2131,27 +2131,27 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-223644</t>
+          <t>I-336665</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-6.779411</t>
+          <t>-6.7878966</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-79.6811213</t>
+          <t>-79.8702939</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Prolongación Avenida Francisco Bolognesi / Calle s / n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2178,27 +2178,27 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-223630</t>
+          <t>I-261576</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-6.7795696</t>
+          <t>-6.7809457</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-79.6801786</t>
+          <t>-79.8370332</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>José Rodriguez Trigoso / Calle s / n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2225,17 +2225,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-642795</t>
+          <t>I-235222</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-6.8209849</t>
+          <t>-6.8409089</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-79.7855517</t>
+          <t>-79.7906501</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2245,7 +2245,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2272,27 +2272,27 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I-36516</t>
+          <t>I-232941</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-6.8810225</t>
+          <t>-6.7699818</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-79.8594709</t>
+          <t>-79.7790817</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Perú / Jirón Leoncio Prado</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2319,27 +2319,27 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-645602</t>
+          <t>I-232878</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-6.8670564</t>
+          <t>-6.7703867</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-79.8900134</t>
+          <t>-79.7830318</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Perú / Calle s / n</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2366,27 +2366,27 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I-645604</t>
+          <t>I-232650</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-6.8664225</t>
+          <t>-6.7700987</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-79.8848045</t>
+          <t>-79.778826</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida San Francisco de Asís / Calle s / n</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2413,27 +2413,27 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I-645605</t>
+          <t>I-232602</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-6.85918</t>
+          <t>-6.7702521</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-79.8868474</t>
+          <t>-79.7821132</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Perú / Calle Los Algarrobos</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -2460,27 +2460,27 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>I-724649</t>
+          <t>I-225128</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-6.8197773</t>
+          <t>-6.7708286</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-79.8947424</t>
+          <t>-79.7870572</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Bolivia / Avenida Perú</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2507,22 +2507,22 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>I-7049</t>
+          <t>I-225105</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-6.7946816</t>
+          <t>-6.770017</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-79.6875053</t>
+          <t>-79.7777271</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida San Francisco de Asís / Calle s / n</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2554,22 +2554,22 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>I-9271</t>
+          <t>I-223920</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-6.7892645</t>
+          <t>-6.6906458</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-79.8469799</t>
+          <t>-79.7052787</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Avenida Chinchaysuyo / Avenida Miguel Grau</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2601,22 +2601,22 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>I-732278</t>
+          <t>I-223918</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-6.8261457</t>
+          <t>-6.6922831</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-79.8756368</t>
+          <t>-79.7036186</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Camino Luya / Calle s / n</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2648,17 +2648,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>I-667432</t>
+          <t>I-223916</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-6.8540783</t>
+          <t>-6.6869884</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-79.8720089</t>
+          <t>-79.705396</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2695,17 +2695,17 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>I-645606</t>
+          <t>I-223904</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-6.860875</t>
+          <t>-6.6902876</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-79.8859891</t>
+          <t>-79.693757</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2742,17 +2742,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>I-645804</t>
+          <t>I-223903</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-6.8750272</t>
+          <t>-6.6908033</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-79.8986587</t>
+          <t>-79.7024575</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2789,17 +2789,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>I-645805</t>
+          <t>I-223644</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-6.8689665</t>
+          <t>-6.779411</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-79.897498</t>
+          <t>-79.6811213</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>I-579094</t>
+          <t>I-223630</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-6.7716644</t>
+          <t>-6.7795696</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-79.7928375</t>
+          <t>-79.6801786</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Avenida San Francisco de Asís / Calle Héroes del Cenepa</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2883,17 +2883,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>I-7050</t>
+          <t>I-223593</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-6.7959262</t>
+          <t>-6.7798068</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-79.6871373</t>
+          <t>-79.6788031</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2930,22 +2930,22 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>I-223593</t>
+          <t>I-181438</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-6.7798068</t>
+          <t>-6.7499562</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-79.6788031</t>
+          <t>-79.6996674</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida El Tren / Calle Tumbes</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2977,27 +2977,27 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>I-181438</t>
+          <t>I-16168</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-6.7499562</t>
+          <t>-6.8216999</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-79.6996674</t>
+          <t>-79.8550922</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Avenida El Tren / Calle Tumbes</t>
+          <t>Carretera Monsefú - Chiclayo / LA-784</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
